--- a/BSI.IT.27.C7_PAM_Recert_Sample_Conclusions.xlsx
+++ b/BSI.IT.27.C7_PAM_Recert_Sample_Conclusions.xlsx
@@ -8,6 +8,7 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Conclusions" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fieldglass Evidence" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1" iterateDelta="0.0001"/>
@@ -17,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <name val="Aptos Narrow"/>
       <family val="2"/>
@@ -58,6 +59,9 @@
     <font>
       <b val="1"/>
       <color rgb="00006100"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="8">
@@ -142,7 +146,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -170,6 +174,7 @@
     <xf numFmtId="0" fontId="7" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1316,10 +1321,11 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Fieldglass evidence placeholder (fill in from the email - do not conclude PASS until filled): Fieldglass email [sender / date - TO INSERT] confirms Work Order [# - TO INSERT] is active, start [date] / end [date] covering the 7/27/2026 SOX and 8/17/2026 CyberArk certification dates</t>
-        </is>
-      </c>
-    </row>
+          <t>Fieldglass evidence: Email 'RE: Request for Fieldglass Evidence - BSI.IT.27.C7 Testing' from Ana Belloso (BSI Procurement) to Edward Morfa, 10/29/2026 13:52 UTC, with Fieldglass search screenshots (image001-006). Not requested/provided for MIA25142, MIA25172, MIA25175, X453396 - their exception (A6) is not an engagement-status question.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5"/>
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
         <is>
@@ -1338,7 +1344,7 @@
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>Fieldglass evidence (to insert from email)</t>
+          <t>Fieldglass evidence</t>
         </is>
       </c>
       <c r="E6" s="7" t="inlineStr">
@@ -1385,7 +1391,7 @@
       </c>
       <c r="D7" s="8" t="inlineStr">
         <is>
-          <t>WO #: [ ]  Start: [ ]  End: [ ]  Email from/date: [ ]</t>
+          <t>Not in Fieldglass request/response - not needed: the exception is the unapproved re-grant, not engagement status.</t>
         </is>
       </c>
       <c r="E7" s="8" t="inlineStr">
@@ -1432,7 +1438,7 @@
       </c>
       <c r="D8" s="8" t="inlineStr">
         <is>
-          <t>WO #: [ ]  Start: [ ]  End: [ ]  Email from/date: [ ]</t>
+          <t>Not in Fieldglass request/response - not needed: the exception is the unapproved re-grant, not engagement status.</t>
         </is>
       </c>
       <c r="E8" s="8" t="inlineStr">
@@ -1479,7 +1485,7 @@
       </c>
       <c r="D9" s="8" t="inlineStr">
         <is>
-          <t>WO #: [ ]  Start: [ ]  End: [ ]  Email from/date: [ ]</t>
+          <t>Not in Fieldglass request/response - not needed: the exception is the unapproved re-grant, not engagement status.</t>
         </is>
       </c>
       <c r="E9" s="8" t="inlineStr">
@@ -1526,7 +1532,7 @@
       </c>
       <c r="D10" s="8" t="inlineStr">
         <is>
-          <t>WO #: [ ]  Start: [ ]  End: [ ]  Email from/date: [ ]</t>
+          <t>Not in Fieldglass request/response - not needed: the exception is the unapproved re-grant, not engagement status.</t>
         </is>
       </c>
       <c r="E10" s="8" t="inlineStr">
@@ -1573,7 +1579,7 @@
       </c>
       <c r="D11" s="8" t="inlineStr">
         <is>
-          <t>WO #: [ ]  Start: [ ]  End: [ ]  Email from/date: [ ]</t>
+          <t>email from BSI Procurement 10/29/2026. Worker SANWK00016501 OPEN 2024-01-01 - 2027-02-28; current WO SANWO00017798 (Rev.18) Confirmed 2026-09-29 - 2027-02-28; buyer ref 100531048; prior record: SANWK00014976 / WO SANWO00016242 Closed 2023-10-08 - 2023-12-31.</t>
         </is>
       </c>
       <c r="E11" s="8" t="inlineStr">
@@ -1588,17 +1594,17 @@
       </c>
       <c r="G11" s="10" t="inlineStr">
         <is>
-          <t>PASS (with observation) - conditional on Fieldglass email</t>
+          <t>PASS (with observation)</t>
         </is>
       </c>
       <c r="H11" s="8" t="inlineStr">
         <is>
-          <t>SanIAM shows IAMS Termination Date 12/31/2024, but the user is still active in AD and approved in both 2026 Q2 certifications. SUS.IAMS.4.2.1.1 makes HR the authoritative source for external users; for contingent workers that HR record is Fieldglass. Fieldglass shows the worker was active through both certification dates, so he was NOT a terminated user and the 4.2.4.2/4.2.4.3 termination SLAs were not triggered. The AD account being disabled is a MORE restrictive state - privileged access via CyberArk/Alero cannot be used without an enabled AD identity - consistent with 4.2.3.1 inactivity disablement. The manager approved access of an active direct contractor, which is what 4.2.5.6 requires. Observation: account has stayed disabled since; manager should confirm continued need or revoke at next cycle.</t>
+          <t>Fieldglass (email from BSI Procurement 10/29/2026) shows Worker SANWK00016501 Status OPEN, period 2024-01-01 - 2027-02-28, SGTO_CYBER BAU_PROTECT_2023, Dept GREXT_000079 Cyber Security, supplier Grupo Santander (SGT). The open period covers every relevant date (8/28/2025, 4/30/2026, 7/27/2026 SOX cert, 8/17/2026 CyberArk cert) and no closed worker record or break in 2025-2026 is shown. The SanIAM IAMS Termination Date of 12/31/2024 does not match any Fieldglass engagement end (the only closed record ended 12/31/2023) - it is stale data, not a separation. Under SUS.IAMS.4.2.1.1 HR (Fieldglass for contingent workers) is the authoritative source, so the user was an ACTIVE workforce member when approved; the termination SLAs in 4.2.4.2 / 4.2.4.3 (App. G) were not triggered, and manager approval in both quarterly certifications satisfies SUS.IAMS.4.2.5.6 and PAM Procedure Section 2 / 4.1.1 C2. AD was disabled at approval and remains disabled at 10/10/2026. Because Fieldglass confirms active engagement, the disablement is an inactivity/restrictive state (SUS.IAMS.4.2.3.1), not a missed termination; a disabled AD identity cannot use the CyberArk/Alero access. Observation: account unused/disabled for an extended period - manager should confirm continued need or revoke at next cycle (least privilege, 4.2.5.1). Evidence limitation (does not change the conclusion): screenshots are search-result views without the report run date/parameters, extension history or approvers requested in the 10/14/2026 email; the current work order revision (Rev.18) shows period 2026-09-29 - 2027-02-28 and a Job Seeker submission on 2026-09-29, so the continuity conclusion rests on the OPEN worker record period.</t>
         </is>
       </c>
       <c r="I11" s="8" t="inlineStr">
         <is>
-          <t>Becomes FAIL if the Fieldglass end date is before 7/27/2026 (user was terminated and approval/retention breaches 4.2.4.3).</t>
+          <t>Would change to FAIL only if the Fieldglass detail/history shows the engagement ended or lapsed before 8/17/2026 (e.g., if the 2026-09-29 work order was a re-hire after a gap).</t>
         </is>
       </c>
     </row>
@@ -1620,7 +1626,7 @@
       </c>
       <c r="D12" s="8" t="inlineStr">
         <is>
-          <t>WO #: [ ]  Start: [ ]  End: [ ]  Email from/date: [ ]</t>
+          <t>email from BSI Procurement 10/29/2026. Worker SANWK00016508 OPEN 2024-01-01 - 2027-02-28; current WO SANWO00017799 (Rev.18) Confirmed 2026-09-29 - 2027-02-28; buyer ref 100531049; prior record: SANWK00014980 / WO SANWO00016246 Closed 2023-10-08 - 2023-12-31.</t>
         </is>
       </c>
       <c r="E12" s="8" t="inlineStr">
@@ -1635,17 +1641,17 @@
       </c>
       <c r="G12" s="10" t="inlineStr">
         <is>
-          <t>PASS - conditional on Fieldglass email</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="H12" s="8" t="inlineStr">
         <is>
-          <t>SanIAM shows IAMS Termination Date 12/31/2024, but the user is still active in AD and approved in both 2026 Q2 certifications. SUS.IAMS.4.2.1.1 makes HR the authoritative source for external users; for contingent workers that HR record is Fieldglass. The open E2 item was only waiting on Fieldglass. The email confirms an active work order covering the review period, so the 12/31/2024 SanIAM date is a stale original contract end date, not a separation. Active contractor + manager approval in both quarterly certs (SOX 7/27/2026, CyberArk 8/17/2026) satisfies 4.2.5.6 and PAM Proc. Section 2 (quarterly line-manager recert). No exception.</t>
+          <t>Fieldglass (email from BSI Procurement 10/29/2026) shows Worker SANWK00016508 Status OPEN, period 2024-01-01 - 2027-02-28, SGTO_CYBER BAU_PROTECT_2023, Dept GREXT_000079 Cyber Security, supplier Grupo Santander (SGT). The open period covers every relevant date (8/28/2025, 4/30/2026, 7/27/2026 SOX cert, 8/17/2026 CyberArk cert) and no closed worker record or break in 2025-2026 is shown. The SanIAM IAMS Termination Date of 12/31/2024 does not match any Fieldglass engagement end (the only closed record ended 12/31/2023) - it is stale data, not a separation. Under SUS.IAMS.4.2.1.1 HR (Fieldglass for contingent workers) is the authoritative source, so the user was an ACTIVE workforce member when approved; the termination SLAs in 4.2.4.2 / 4.2.4.3 (App. G) were not triggered, and manager approval in both quarterly certifications satisfies SUS.IAMS.4.2.5.6 and PAM Procedure Section 2 / 4.1.1 C2. The E2 item pending Fieldglass is closed. No exception. Evidence limitation (does not change the conclusion): screenshots are search-result views without the report run date/parameters, extension history or approvers requested in the 10/14/2026 email; the current work order revision (Rev.18) shows period 2026-09-29 - 2027-02-28 and a Job Seeker submission on 2026-09-29, so the continuity conclusion rests on the OPEN worker record period.</t>
         </is>
       </c>
       <c r="I12" s="8" t="inlineStr">
         <is>
-          <t>FAIL if Fieldglass end date precedes the certification dates.</t>
+          <t>Would change to FAIL only if the Fieldglass detail/history shows the engagement ended or lapsed before 8/17/2026 (e.g., if the 2026-09-29 work order was a re-hire after a gap).</t>
         </is>
       </c>
     </row>
@@ -1667,7 +1673,7 @@
       </c>
       <c r="D13" s="8" t="inlineStr">
         <is>
-          <t>WO #: [ ]  Start: [ ]  End: [ ]  Email from/date: [ ]</t>
+          <t>email from BSI Procurement 10/29/2026. Worker SANWK00016502 OPEN 2024-01-01 - 2027-02-28; current WO SANWO00017797 (Rev.18) Confirmed 2026-09-29 - 2027-02-28; buyer ref 100531050; prior record: SANWK00014979 / WO SANWO00016245 Closed 2023-10-08 - 2023-12-31.</t>
         </is>
       </c>
       <c r="E13" s="8" t="inlineStr">
@@ -1682,17 +1688,17 @@
       </c>
       <c r="G13" s="10" t="inlineStr">
         <is>
-          <t>PASS - conditional on Fieldglass email</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="H13" s="8" t="inlineStr">
         <is>
-          <t>SanIAM shows IAMS Termination Date 12/31/2024, but the user is still active in AD and approved in both 2026 Q2 certifications. SUS.IAMS.4.2.1.1 makes HR the authoritative source for external users; for contingent workers that HR record is Fieldglass. Fieldglass confirms active engagement through the review period; the 12/31/2024 date is stale. Manager approval of an active contractor in both quarterly certifications meets 4.2.5.6 and the PAM Procedure. No exception.</t>
+          <t>Fieldglass (email from BSI Procurement 10/29/2026) shows Worker SANWK00016502 Status OPEN, period 2024-01-01 - 2027-02-28, SGTO_CYBER BAU_PROTECT_2023, Dept GREXT_000079 Cyber Security, supplier Grupo Santander (SGT). The open period covers every relevant date (8/28/2025, 4/30/2026, 7/27/2026 SOX cert, 8/17/2026 CyberArk cert) and no closed worker record or break in 2025-2026 is shown. The SanIAM IAMS Termination Date of 12/31/2024 does not match any Fieldglass engagement end (the only closed record ended 12/31/2023) - it is stale data, not a separation. Under SUS.IAMS.4.2.1.1 HR (Fieldglass for contingent workers) is the authoritative source, so the user was an ACTIVE workforce member when approved; the termination SLAs in 4.2.4.2 / 4.2.4.3 (App. G) were not triggered, and manager approval in both quarterly certifications satisfies SUS.IAMS.4.2.5.6 and PAM Procedure Section 2 / 4.1.1 C2. The E2 item pending Fieldglass is closed. No exception. Evidence limitation (does not change the conclusion): screenshots are search-result views without the report run date/parameters, extension history or approvers requested in the 10/14/2026 email; the current work order revision (Rev.18) shows period 2026-09-29 - 2027-02-28 and a Job Seeker submission on 2026-09-29, so the continuity conclusion rests on the OPEN worker record period.</t>
         </is>
       </c>
       <c r="I13" s="8" t="inlineStr">
         <is>
-          <t>FAIL if Fieldglass end date precedes the certification dates.</t>
+          <t>Would change to FAIL only if the Fieldglass detail/history shows the engagement ended or lapsed before 8/17/2026 (e.g., if the 2026-09-29 work order was a re-hire after a gap).</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1720,7 @@
       </c>
       <c r="D14" s="8" t="inlineStr">
         <is>
-          <t>WO #: [ ]  Start: [ ]  End: [ ]  Email from/date: [ ]</t>
+          <t>email from BSI Procurement 10/29/2026. Worker SANWK00016503 OPEN 2024-01-01 - 2027-02-28; current WO SANWO00017800 (Rev.18) Confirmed 2026-09-29 - 2027-02-28; buyer ref 100531051; prior record: SANWK00014977 / WO SANWO00016243 Closed 2023-10-08 - 2023-12-31.</t>
         </is>
       </c>
       <c r="E14" s="8" t="inlineStr">
@@ -1729,17 +1735,17 @@
       </c>
       <c r="G14" s="10" t="inlineStr">
         <is>
-          <t>PASS - conditional on Fieldglass email</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="H14" s="8" t="inlineStr">
         <is>
-          <t>SanIAM shows IAMS Termination Date 12/31/2024, but the user is still active in AD and approved in both 2026 Q2 certifications. SUS.IAMS.4.2.1.1 makes HR the authoritative source for external users; for contingent workers that HR record is Fieldglass. Fieldglass confirms active engagement through the review period; the 12/31/2024 date is stale. Manager approval of an active contractor in both quarterly certifications meets 4.2.5.6 and the PAM Procedure. No exception.</t>
+          <t>Fieldglass (email from BSI Procurement 10/29/2026) shows Worker SANWK00016503 Status OPEN, period 2024-01-01 - 2027-02-28, SGTO_CYBER BAU_PROTECT_2023, Dept GREXT_000079 Cyber Security, supplier Grupo Santander (SGT). The open period covers every relevant date (8/28/2025, 4/30/2026, 7/27/2026 SOX cert, 8/17/2026 CyberArk cert) and no closed worker record or break in 2025-2026 is shown. The SanIAM IAMS Termination Date of 12/31/2024 does not match any Fieldglass engagement end (the only closed record ended 12/31/2023) - it is stale data, not a separation. Under SUS.IAMS.4.2.1.1 HR (Fieldglass for contingent workers) is the authoritative source, so the user was an ACTIVE workforce member when approved; the termination SLAs in 4.2.4.2 / 4.2.4.3 (App. G) were not triggered, and manager approval in both quarterly certifications satisfies SUS.IAMS.4.2.5.6 and PAM Procedure Section 2 / 4.1.1 C2. The E2 item pending Fieldglass is closed. No exception. Evidence limitation (does not change the conclusion): screenshots are search-result views without the report run date/parameters, extension history or approvers requested in the 10/14/2026 email; the current work order revision (Rev.18) shows period 2026-09-29 - 2027-02-28 and a Job Seeker submission on 2026-09-29, so the continuity conclusion rests on the OPEN worker record period.</t>
         </is>
       </c>
       <c r="I14" s="8" t="inlineStr">
         <is>
-          <t>FAIL if Fieldglass end date precedes the certification dates.</t>
+          <t>Would change to FAIL only if the Fieldglass detail/history shows the engagement ended or lapsed before 8/17/2026 (e.g., if the 2026-09-29 work order was a re-hire after a gap).</t>
         </is>
       </c>
     </row>
@@ -1761,7 +1767,7 @@
       </c>
       <c r="D15" s="8" t="inlineStr">
         <is>
-          <t>WO #: [ ]  Start: [ ]  End: [ ]  Email from/date: [ ]</t>
+          <t>email from BSI Procurement 10/29/2026. Worker SANWK00016311 OPEN 2023-12-28 - 2027-02-28; current WO SANWO00017821 (Rev.18) Confirmed 2026-09-29 - 2027-02-28; buyer ref 100592069; prior record: None shown.</t>
         </is>
       </c>
       <c r="E15" s="8" t="inlineStr">
@@ -1776,17 +1782,17 @@
       </c>
       <c r="G15" s="10" t="inlineStr">
         <is>
-          <t>PASS (with observation) - conditional on Fieldglass email</t>
+          <t>PASS (with observation)</t>
         </is>
       </c>
       <c r="H15" s="8" t="inlineStr">
         <is>
-          <t>SanIAM shows IAMS Termination Date 12/31/2024, but the user is still active in AD and approved in both 2026 Q2 certifications. SUS.IAMS.4.2.1.1 makes HR the authoritative source for external users; for contingent workers that HR record is Fieldglass. Fieldglass shows an active work order across the period, so the AD disablement on 05/15/2026 was an inactivity/temporary disablement (4.2.3.1), not a termination; re-enablement by 10/10/2026 is consistent with continued engagement. Approving entitlements of an active contractor whose AD was temporarily disabled is appropriate (4.2.5.6); a disabled AD account cannot use the privileged access. Observation: obtain the re-enable ticket to evidence the AD re-activation was authorized.</t>
+          <t>Fieldglass (email from BSI Procurement 10/29/2026) shows Worker SANWK00016311 Status OPEN, period 2023-12-28 - 2027-02-28, SGTO_CYBER BAU_PROTECT_2023, Dept GREXT_000079 Cyber Security, supplier Grupo Santander (SGT). The open period covers every relevant date (8/28/2025, 4/30/2026, 7/27/2026 SOX cert, 8/17/2026 CyberArk cert) and no closed worker record or break in 2025-2026 is shown. The SanIAM IAMS Termination Date of 12/31/2024 does not match any Fieldglass engagement end (the only closed record ended 12/31/2023) - it is stale data, not a separation. Under SUS.IAMS.4.2.1.1 HR (Fieldglass for contingent workers) is the authoritative source, so the user was an ACTIVE workforce member when approved; the termination SLAs in 4.2.4.2 / 4.2.4.3 (App. G) were not triggered, and manager approval in both quarterly certifications satisfies SUS.IAMS.4.2.5.6 and PAM Procedure Section 2 / 4.1.1 C2. AD FALSE on 05/15/2026 and TRUE on 10/10/2026: Fieldglass shows no engagement end or gap in April-May 2026, so the disablement was not a termination (4.2.3.1 inactivity) and approval of an active contractor's access was appropriate. Observation: obtain the AD re-enable ticket to evidence the re-activation was authorized. Note: Fieldglass also lists an Active Santander US employee 'Harris, Richard (n222712)', Hiring Manager, Cyber Security Engineering - confirm identity link (not needed for the conclusion). Evidence limitation (does not change the conclusion): screenshots are search-result views without the report run date/parameters, extension history or approvers requested in the 10/14/2026 email; the current work order revision (Rev.18) shows period 2026-09-29 - 2027-02-28 and a Job Seeker submission on 2026-09-29, so the continuity conclusion rests on the OPEN worker record period.</t>
         </is>
       </c>
       <c r="I15" s="8" t="inlineStr">
         <is>
-          <t>FAIL if Fieldglass end date precedes 7/27/2026, or if the AD re-enable has no authorized request.</t>
+          <t>Would change to FAIL only if the Fieldglass detail/history shows the engagement ended or lapsed before 8/17/2026 (e.g., if the 2026-09-29 work order was a re-hire after a gap).</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1814,7 @@
       </c>
       <c r="D16" s="8" t="inlineStr">
         <is>
-          <t>WO #: [ ]  Start: [ ]  End: [ ]  Email from/date: [ ]</t>
+          <t>email from BSI Procurement 10/29/2026. Worker SANWK00016313 OPEN 2023-12-28 - 2027-02-28; current WO SANWO00017820 (Rev.18) Confirmed 2026-09-29 - 2027-02-28; buyer ref 100592068; prior record: None shown.</t>
         </is>
       </c>
       <c r="E16" s="8" t="inlineStr">
@@ -1823,31 +1829,595 @@
       </c>
       <c r="G16" s="10" t="inlineStr">
         <is>
-          <t>PASS (with observation) - conditional on Fieldglass email</t>
+          <t>PASS (with observation)</t>
         </is>
       </c>
       <c r="H16" s="8" t="inlineStr">
         <is>
-          <t>SanIAM shows IAMS Termination Date 12/31/2024, but the user is still active in AD and approved in both 2026 Q2 certifications. SUS.IAMS.4.2.1.1 makes HR the authoritative source for external users; for contingent workers that HR record is Fieldglass. Same as MIA25249: Fieldglass evidences active engagement, so the 05/15/2026 disablement was not a termination and the approvals are appropriate. Observations: (1) blank AD employeeNumber means AD is not fully synchronized with HR (4.2.1.1) - remediate by populating the Fieldglass worker ID; (2) evidence the AD re-enable request.</t>
+          <t>Fieldglass (email from BSI Procurement 10/29/2026) shows Worker SANWK00016313 Status OPEN, period 2023-12-28 - 2027-02-28, SGTO_CYBER BAU_PROTECT_2023, Dept GREXT_000079 Cyber Security, supplier Grupo Santander (SGT). The open period covers every relevant date (8/28/2025, 4/30/2026, 7/27/2026 SOX cert, 8/17/2026 CyberArk cert) and no closed worker record or break in 2025-2026 is shown. The SanIAM IAMS Termination Date of 12/31/2024 does not match any Fieldglass engagement end (the only closed record ended 12/31/2023) - it is stale data, not a separation. Under SUS.IAMS.4.2.1.1 HR (Fieldglass for contingent workers) is the authoritative source, so the user was an ACTIVE workforce member when approved; the termination SLAs in 4.2.4.2 / 4.2.4.3 (App. G) were not triggered, and manager approval in both quarterly certifications satisfies SUS.IAMS.4.2.5.6 and PAM Procedure Section 2 / 4.1.1 C2. AD FALSE on 05/15/2026 and TRUE on 10/10/2026: no engagement end or gap shown, so not a termination. Observations: (1) AD employeeNumber is blank - populate the Fieldglass worker ID so AD is synchronized with HR (4.2.1.1); (2) obtain the AD re-enable ticket. Fieldglass also lists Workforce ID SGTOWF00003892 and an Active employee 'Ackley, Kevin (n67450)', Cyber Security Engineering - confirm identity link. Evidence limitation (does not change the conclusion): screenshots are search-result views without the report run date/parameters, extension history or approvers requested in the 10/14/2026 email; the current work order revision (Rev.18) shows period 2026-09-29 - 2027-02-28 and a Job Seeker submission on 2026-09-29, so the continuity conclusion rests on the OPEN worker record period.</t>
         </is>
       </c>
       <c r="I16" s="8" t="inlineStr">
         <is>
-          <t>FAIL if Fieldglass end date precedes 7/27/2026, or if the AD re-enable has no authorized request.</t>
-        </is>
-      </c>
-    </row>
+          <t>Would change to FAIL only if the Fieldglass detail/history shows the engagement ended or lapsed before 8/17/2026 (e.g., if the 2026-09-29 work order was a re-hire after a gap).</t>
+        </is>
+      </c>
+    </row>
+    <row r="17"/>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Summary: 6 PASS (conditional on Fieldglass email: MIA25103, MIA25104, MIA25105, MIA25106, MIA25249, MIA25250); 4 FAIL - A6 removal not sustained (MIA25142, MIA25172, MIA25175, X453396).</t>
+          <t>Summary: 6 PASS based on Fieldglass (MIA25104, MIA25105, MIA25106 clean; MIA25103, MIA25249, MIA25250 with observations); 4 FAIL - A6 removal not sustained (MIA25142, MIA25172, MIA25175, X453396). Fieldglass also covered MIA25251 Ashish Rimal (not in this sample).</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Overall observation: SanIAM IAMS termination dates (12/31/2024) are not synchronized with Fieldglass end dates (SUS.IAMS.4.2.1.1) - recommend a Fieldglass-to-SanIAM feed/reconciliation.</t>
+          <t>Overall observation: SanIAM IAMS termination date 12/31/2024 matches no Fieldglass engagement end (open records run to 2027-02-28; prior closed records ended 12/31/2023) - SanIAM is not synchronized with Fieldglass (SUS.IAMS.4.2.1.1). Recommend a Fieldglass-to-SanIAM end-date reconciliation.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:M12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="9" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="30" customWidth="1" min="11" max="11"/>
+    <col width="45" customWidth="1" min="12" max="12"/>
+    <col width="50" customWidth="1" min="13" max="13"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="11" t="inlineStr">
+        <is>
+          <t>Source: Email 'RE: Request for Fieldglass Evidence - BSI.IT.27.C7 Testing' from Ana Belloso (BSI Procurement) to Edward Morfa, 10/29/2026 13:52 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="7" t="inlineStr">
+        <is>
+          <t>Account</t>
+        </is>
+      </c>
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C3" s="7" t="inlineStr">
+        <is>
+          <t>Screenshot</t>
+        </is>
+      </c>
+      <c r="D3" s="7" t="inlineStr">
+        <is>
+          <t>Worker ID</t>
+        </is>
+      </c>
+      <c r="E3" s="7" t="inlineStr">
+        <is>
+          <t>Worker status</t>
+        </is>
+      </c>
+      <c r="F3" s="7" t="inlineStr">
+        <is>
+          <t>Worker period</t>
+        </is>
+      </c>
+      <c r="G3" s="7" t="inlineStr">
+        <is>
+          <t>Current Work Order</t>
+        </is>
+      </c>
+      <c r="H3" s="7" t="inlineStr">
+        <is>
+          <t>WO status</t>
+        </is>
+      </c>
+      <c r="I3" s="7" t="inlineStr">
+        <is>
+          <t>WO period</t>
+        </is>
+      </c>
+      <c r="J3" s="7" t="inlineStr">
+        <is>
+          <t>Buyer ref</t>
+        </is>
+      </c>
+      <c r="K3" s="7" t="inlineStr">
+        <is>
+          <t>Job Seeker (submitted)</t>
+        </is>
+      </c>
+      <c r="L3" s="7" t="inlineStr">
+        <is>
+          <t>Prior closed record</t>
+        </is>
+      </c>
+      <c r="M3" s="7" t="inlineStr">
+        <is>
+          <t>Other matches in search</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="8" t="inlineStr">
+        <is>
+          <t>MIA25103</t>
+        </is>
+      </c>
+      <c r="B4" s="8" t="inlineStr">
+        <is>
+          <t>Ivan Ramirez Gonzalez</t>
+        </is>
+      </c>
+      <c r="C4" s="8" t="inlineStr">
+        <is>
+          <t>image001</t>
+        </is>
+      </c>
+      <c r="D4" s="8" t="inlineStr">
+        <is>
+          <t>SANWK00016501</t>
+        </is>
+      </c>
+      <c r="E4" s="8" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="F4" s="8" t="inlineStr">
+        <is>
+          <t>2024-01-01 - 2027-02-28</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>SANWO00017798 (Rev.18)</t>
+        </is>
+      </c>
+      <c r="H4" s="8" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="I4" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-29 - 2027-02-28</t>
+        </is>
+      </c>
+      <c r="J4" s="8" t="inlineStr">
+        <is>
+          <t>100531048</t>
+        </is>
+      </c>
+      <c r="K4" s="8" t="inlineStr">
+        <is>
+          <t>SGTOJS00000382 (2026-09-29 12:04 PM)</t>
+        </is>
+      </c>
+      <c r="L4" s="8" t="inlineStr">
+        <is>
+          <t>SANWK00014976 / SANWO00016242, Miami - Unassigned Workers, 2023-10-08 - 2023-12-31, Closed</t>
+        </is>
+      </c>
+      <c r="M4" s="8" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="8" t="inlineStr">
+        <is>
+          <t>MIA25104</t>
+        </is>
+      </c>
+      <c r="B5" s="8" t="inlineStr">
+        <is>
+          <t>Jefferson Paez Venegas</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="inlineStr">
+        <is>
+          <t>image002</t>
+        </is>
+      </c>
+      <c r="D5" s="8" t="inlineStr">
+        <is>
+          <t>SANWK00016508</t>
+        </is>
+      </c>
+      <c r="E5" s="8" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="F5" s="8" t="inlineStr">
+        <is>
+          <t>2024-01-01 - 2027-02-28</t>
+        </is>
+      </c>
+      <c r="G5" s="8" t="inlineStr">
+        <is>
+          <t>SANWO00017799 (Rev.18)</t>
+        </is>
+      </c>
+      <c r="H5" s="8" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="I5" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-29 - 2027-02-28</t>
+        </is>
+      </c>
+      <c r="J5" s="8" t="inlineStr">
+        <is>
+          <t>100531049</t>
+        </is>
+      </c>
+      <c r="K5" s="8" t="inlineStr">
+        <is>
+          <t>SGTOJS00000383 (2026-09-29 12:05 PM)</t>
+        </is>
+      </c>
+      <c r="L5" s="8" t="inlineStr">
+        <is>
+          <t>SANWK00014980 / SANWO00016246, 2023-10-08 - 2023-12-31, Closed</t>
+        </is>
+      </c>
+      <c r="M5" s="8" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>MIA25105</t>
+        </is>
+      </c>
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t>David Serrano Aguirre</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>image003</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>SANWK00016502</t>
+        </is>
+      </c>
+      <c r="E6" s="8" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="F6" s="8" t="inlineStr">
+        <is>
+          <t>2024-01-01 - 2027-02-28</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>SANWO00017797 (Rev.18)</t>
+        </is>
+      </c>
+      <c r="H6" s="8" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="I6" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-29 - 2027-02-28</t>
+        </is>
+      </c>
+      <c r="J6" s="8" t="inlineStr">
+        <is>
+          <t>100531050</t>
+        </is>
+      </c>
+      <c r="K6" s="8" t="inlineStr">
+        <is>
+          <t>SGTOJS00000381 (2026-09-29 12:04 PM)</t>
+        </is>
+      </c>
+      <c r="L6" s="8" t="inlineStr">
+        <is>
+          <t>SANWK00014979 / SANWO00016245, 2023-10-08 - 2023-12-31, Closed</t>
+        </is>
+      </c>
+      <c r="M6" s="8" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>MIA25106</t>
+        </is>
+      </c>
+      <c r="B7" s="8" t="inlineStr">
+        <is>
+          <t>Maiko Vazquez Arias</t>
+        </is>
+      </c>
+      <c r="C7" s="8" t="inlineStr">
+        <is>
+          <t>image004</t>
+        </is>
+      </c>
+      <c r="D7" s="8" t="inlineStr">
+        <is>
+          <t>SANWK00016503</t>
+        </is>
+      </c>
+      <c r="E7" s="8" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="F7" s="8" t="inlineStr">
+        <is>
+          <t>2024-01-01 - 2027-02-28</t>
+        </is>
+      </c>
+      <c r="G7" s="8" t="inlineStr">
+        <is>
+          <t>SANWO00017800 (Rev.18)</t>
+        </is>
+      </c>
+      <c r="H7" s="8" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="I7" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-29 - 2027-02-28</t>
+        </is>
+      </c>
+      <c r="J7" s="8" t="inlineStr">
+        <is>
+          <t>100531051</t>
+        </is>
+      </c>
+      <c r="K7" s="8" t="inlineStr">
+        <is>
+          <t>SGTOJS00000384 (2026-09-29 12:05 PM)</t>
+        </is>
+      </c>
+      <c r="L7" s="8" t="inlineStr">
+        <is>
+          <t>SANWK00014977 / SANWO00016243, 2023-10-08 - 2023-12-31, Closed</t>
+        </is>
+      </c>
+      <c r="M7" s="8" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>MIA25249</t>
+        </is>
+      </c>
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>Richard Harris</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>image005</t>
+        </is>
+      </c>
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t>SANWK00016311</t>
+        </is>
+      </c>
+      <c r="E8" s="8" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="F8" s="8" t="inlineStr">
+        <is>
+          <t>2023-12-28 - 2027-02-28</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>SANWO00017821 (Rev.18)</t>
+        </is>
+      </c>
+      <c r="H8" s="8" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="I8" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-29 - 2027-02-28</t>
+        </is>
+      </c>
+      <c r="J8" s="8" t="inlineStr">
+        <is>
+          <t>100592069</t>
+        </is>
+      </c>
+      <c r="K8" s="8" t="inlineStr">
+        <is>
+          <t>SGTOJS00000391 (2026-09-29 12:05 PM)</t>
+        </is>
+      </c>
+      <c r="L8" s="8" t="inlineStr">
+        <is>
+          <t>None shown</t>
+        </is>
+      </c>
+      <c r="M8" s="8" t="inlineStr">
+        <is>
+          <t>Employee Harris, Richard (n222712) Active, Hiring Manager, ISB00_73097 Cyber Security Eng. &amp; Arch.; other Harris employees unrelated</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>MIA25250</t>
+        </is>
+      </c>
+      <c r="B9" s="8" t="inlineStr">
+        <is>
+          <t>Kevin Ackley</t>
+        </is>
+      </c>
+      <c r="C9" s="8" t="inlineStr">
+        <is>
+          <t>image006</t>
+        </is>
+      </c>
+      <c r="D9" s="8" t="inlineStr">
+        <is>
+          <t>SANWK00016313</t>
+        </is>
+      </c>
+      <c r="E9" s="8" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="F9" s="8" t="inlineStr">
+        <is>
+          <t>2023-12-28 - 2027-02-28</t>
+        </is>
+      </c>
+      <c r="G9" s="8" t="inlineStr">
+        <is>
+          <t>SANWO00017820 (Rev.18)</t>
+        </is>
+      </c>
+      <c r="H9" s="8" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="I9" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-29 - 2027-02-28</t>
+        </is>
+      </c>
+      <c r="J9" s="8" t="inlineStr">
+        <is>
+          <t>100592068</t>
+        </is>
+      </c>
+      <c r="K9" s="8" t="inlineStr">
+        <is>
+          <t>SGTOJS00000390 (2026-09-29 12:05 PM)</t>
+        </is>
+      </c>
+      <c r="L9" s="8" t="inlineStr">
+        <is>
+          <t>None shown</t>
+        </is>
+      </c>
+      <c r="M9" s="8" t="inlineStr">
+        <is>
+          <t>Workforce SGTOWF00003892; Employee Ackley, Kevin (n67450) Active, Hiring Manager, ISB00_73097; Ackley, Michelle unrelated</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>MIA25251</t>
+        </is>
+      </c>
+      <c r="B10" s="8" t="inlineStr">
+        <is>
+          <t>Ashish Rimal (not in sample)</t>
+        </is>
+      </c>
+      <c r="C10" s="8" t="inlineStr">
+        <is>
+          <t>image007</t>
+        </is>
+      </c>
+      <c r="D10" s="8" t="inlineStr">
+        <is>
+          <t>SANWK00016312</t>
+        </is>
+      </c>
+      <c r="E10" s="8" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="F10" s="8" t="inlineStr">
+        <is>
+          <t>2023-12-28 - 2027-02-28</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>SANWO00017819 (Rev.18)</t>
+        </is>
+      </c>
+      <c r="H10" s="8" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="I10" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-29 - 2027-02-28</t>
+        </is>
+      </c>
+      <c r="J10" s="8" t="inlineStr">
+        <is>
+          <t>100592070</t>
+        </is>
+      </c>
+      <c r="K10" s="8" t="inlineStr">
+        <is>
+          <t>SGTOJS00000389 (2026-09-29 12:05 PM)</t>
+        </is>
+      </c>
+      <c r="L10" s="8" t="inlineStr">
+        <is>
+          <t>None shown</t>
+        </is>
+      </c>
+      <c r="M10" s="8" t="inlineStr">
+        <is>
+          <t>Employee Rimal, Ashish (n600486) Active, ISB00_73097</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Common to all: Title SGTO_CYBER BAU_PROTECT_2023; Dept GREXT_000079 Cyber Security; Supplier Grupo Santander (SGT); Location Brickell Plaza-Corp (US06374); Job Code USA_SOVOR_EXT024; Job Posting SANTQ00001069.</t>
         </is>
       </c>
     </row>

--- a/BSI.IT.27.C7_PAM_Recert_Sample_Conclusions.xlsx
+++ b/BSI.IT.27.C7_PAM_Recert_Sample_Conclusions.xlsx
@@ -146,7 +146,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -175,6 +175,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1283,578 +1286,625 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I19"/>
+  <dimension ref="A1:J18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="30" customWidth="1" min="4" max="4"/>
-    <col width="55" customWidth="1" min="5" max="5"/>
-    <col width="40" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
-    <col width="80" customWidth="1" min="8" max="8"/>
-    <col width="40" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="38" customWidth="1" min="3" max="3"/>
+    <col width="38" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="6" max="6"/>
+    <col width="36" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="70" customWidth="1" min="9" max="9"/>
+    <col width="40" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="6" t="inlineStr">
         <is>
-          <t>BSI.IT.27.C7 - PAM Recertification sample: per-account conclusions</t>
+          <t>BSI.IT.27.C7 Network Device Admin Account Review - per-account conclusions (testing period 07/01/2025 - 06/30/2026)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026 Q2 PAM recert: SOX Manager cert launched 7/27/2026; CyberArk Manager cert 8/17/2026; AD status as of 10/10/2026</t>
+          <t>Uses every certification in BSI.IT.27.C7_Testing_Package_2: in-period samples 2025 Q3 (E04, decided 8/28/2025) and 2026 Q1 (E05, decided 4/30/2026) for CISCO Network Administrators and ISEAdmin; 2026 Q2 SOX/CyberArk Manager certs (E07, after period end) as supporting/response evidence; Fieldglass email E10.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Standards in force: IAM Standard v10.0 (approved 09.29.2025) for the 7/27/2026 SOX cert; v11.0 (approved 07.28.2026) for the 8/17/2026 CyberArk cert - requirement IDs below are identical in both versions. PAM Recertification Procedure v2.0 (04/22/2026).</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Fieldglass evidence: Email 'RE: Request for Fieldglass Evidence - BSI.IT.27.C7 Testing' from Ana Belloso (BSI Procurement) to Edward Morfa, 10/29/2026 13:52 UTC, with Fieldglass search screenshots (image001-006). Not requested/provided for MIA25142, MIA25172, MIA25175, X453396 - their exception (A6) is not an engagement-status question.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5"/>
+          <t>Account result rule: FAIL if an exception remains in either in-period sample. Standards: IAM Std v10.0 (09/29/2025) in force for both samples; v11.0 for 2026 Q2; PAM Recertification Procedure v2.0 (04/22/2026).</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="12" t="inlineStr">
+        <is>
+          <t>Account</t>
+        </is>
+      </c>
+      <c r="B5" s="12" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C5" s="12" t="inlineStr">
+        <is>
+          <t>2025 Q3 cert (Sample 1, decided 8/28/2025, AD 11/25/2025)</t>
+        </is>
+      </c>
+      <c r="D5" s="12" t="inlineStr">
+        <is>
+          <t>2026 Q1 cert (Sample 2, decided 4/30/2026, AD 05/15/2026)</t>
+        </is>
+      </c>
+      <c r="E5" s="12" t="inlineStr">
+        <is>
+          <t>2026 Q2 certs (7/27/2026 SOX, 8/17/2026 CyberArk) - after period, supporting only</t>
+        </is>
+      </c>
+      <c r="F5" s="12" t="inlineStr">
+        <is>
+          <t>Fieldglass (email 10/29/2026)</t>
+        </is>
+      </c>
+      <c r="G5" s="12" t="inlineStr">
+        <is>
+          <t>Policy references</t>
+        </is>
+      </c>
+      <c r="H5" s="12" t="inlineStr">
+        <is>
+          <t>Conclusion</t>
+        </is>
+      </c>
+      <c r="I5" s="12" t="inlineStr">
+        <is>
+          <t>Rationale</t>
+        </is>
+      </c>
+      <c r="J5" s="12" t="inlineStr">
+        <is>
+          <t>What would change it</t>
+        </is>
+      </c>
+    </row>
     <row r="6">
-      <c r="A6" s="7" t="inlineStr">
-        <is>
-          <t>Account</t>
-        </is>
-      </c>
-      <c r="B6" s="7" t="inlineStr">
-        <is>
-          <t>Name</t>
-        </is>
-      </c>
-      <c r="C6" s="7" t="inlineStr">
-        <is>
-          <t>Review period / certifications</t>
-        </is>
-      </c>
-      <c r="D6" s="7" t="inlineStr">
-        <is>
-          <t>Fieldglass evidence</t>
-        </is>
-      </c>
-      <c r="E6" s="7" t="inlineStr">
-        <is>
-          <t>Key facts from sample</t>
-        </is>
-      </c>
-      <c r="F6" s="7" t="inlineStr">
-        <is>
-          <t>Policy references</t>
-        </is>
-      </c>
-      <c r="G6" s="7" t="inlineStr">
-        <is>
-          <t>Conclusion</t>
-        </is>
-      </c>
-      <c r="H6" s="7" t="inlineStr">
-        <is>
-          <t>Rationale</t>
-        </is>
-      </c>
-      <c r="I6" s="7" t="inlineStr">
-        <is>
-          <t>What would change the conclusion</t>
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>MIA25142</t>
+        </is>
+      </c>
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t>Miguel Nieves Nieves</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>Cisco Network Admins + ISEAdmin REVOKED; removed 09/02/2025 (Netwrix) = 2 bd, within SLA. Back in both groups in AD 11/25/2025 -&gt; removal not sustained (A6).</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>Both groups APPROVED - re-grant approved with no request (A5-E3). IAMS term 12/31/2024 (E2).</t>
+        </is>
+      </c>
+      <c r="E6" s="8" t="inlineStr">
+        <is>
+          <t>Approved (SOX rows 98-100; CyberArk 431-433) - access still held.</t>
+        </is>
+      </c>
+      <c r="F6" s="8" t="inlineStr">
+        <is>
+          <t>Not requested / not provided</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>SUS.IAMS.4.2.5.7, 4.2.5.21 (30 bd SLA), 4.2.3.4 (re-grant needs request + manager + 2nd-level approval); PAM Proc. 4.1.1 C3-C4, sec. 4.2, sec. 8 step 10; 4.2.1.1</t>
+        </is>
+      </c>
+      <c r="H6" s="9" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="I6" s="8" t="inlineStr">
+        <is>
+          <t>Revocation was timely but did not stay in place, and the re-added access was approved in 2026 Q1 without an approved access request. Fieldglass was not obtained for this account, so E2 (IAMS term 12/31/2024) also remains open.</t>
+        </is>
+      </c>
+      <c r="J6" s="8" t="inlineStr">
+        <is>
+          <t>Netwrix 'member added' event + approved ServiceNow request for the re-grant; Fieldglass record.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="8" t="inlineStr">
         <is>
-          <t>MIA25142</t>
+          <t>MIA25172</t>
         </is>
       </c>
       <c r="B7" s="8" t="inlineStr">
         <is>
-          <t>Miguel Nieves Nieves</t>
+          <t>Juan Hernandez Ruiz</t>
         </is>
       </c>
       <c r="C7" s="8" t="inlineStr">
         <is>
-          <t>SOX Mgr 7/27/2026; CyberArk Mgr 8/17/2026</t>
+          <t>Cisco Network Admins REVOKED; removed 09/02/2025 = 2 bd, within SLA. Back in AD 11/25/2025 -&gt; not sustained (A6).</t>
         </is>
       </c>
       <c r="D7" s="8" t="inlineStr">
         <is>
-          <t>Not in Fieldglass request/response - not needed: the exception is the unapproved re-grant, not engagement status.</t>
+          <t>Cisco Network Admins APPROVED - re-grant without request (A5-E3). Also appears in ISEAdmin, where it was not a member in 2025 Q3 - no request seen for that add.</t>
         </is>
       </c>
       <c r="E7" s="8" t="inlineStr">
         <is>
-          <t>Approved: SOX Mgr rows 98-100; CyberArk Mgr rows 431-433; Alero_Consultant_MIA25142 safe (12 rows) Approved. AD enabled TRUE. IAMS term date 12/31/2024, correlated. Prior cycle: Manager REVOKED 8/28/2025, removed 9/2/2025, then access RE-GRANTED. No ServiceNow re-grant request/approval, removal ticket or Netwrix evidence in any tab.</t>
+          <t>Approved (SOX 140-142; CyberArk 467-468). Identity not correlated (Identity = account ID).</t>
         </is>
       </c>
       <c r="F7" s="8" t="inlineStr">
         <is>
-          <t>SUS.IAMS.4.2.1.1; 4.2.3.4 (Privileged Access Change - request, manager validation, 2nd-level approval, documented mechanism); 4.2.5.7 (access denied if any reviewer denies); 4.2.5.21; PAM Proc. 4.1.1 C3/C4, Section 4.2 Monitoring</t>
-        </is>
-      </c>
-      <c r="G7" s="9" t="inlineStr">
+          <t>Not requested / not provided</t>
+        </is>
+      </c>
+      <c r="G7" s="8" t="inlineStr">
+        <is>
+          <t>SUS.IAMS.4.2.5.7, 4.2.5.21 (30 bd SLA), 4.2.3.4 (re-grant needs request + manager + 2nd-level approval); PAM Proc. 4.1.1 C3-C4, sec. 4.2, sec. 8 step 10; 4.2.1.1, 4.2.5.6 (uncorrelated accounts)</t>
+        </is>
+      </c>
+      <c r="H7" s="9" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
       </c>
-      <c r="H7" s="8" t="inlineStr">
-        <is>
-          <t>SanIAM shows IAMS Termination Date 12/31/2024, but the user is still active in AD and approved in both 2026 Q2 certifications. SUS.IAMS.4.2.1.1 makes HR the authoritative source for external users; for contingent workers that HR record is Fieldglass. The Fieldglass email resolves the identity/termination question (E2): the 12/31/2024 date is a stale contract end date, the contractor is active, so the 2026 approvals are not approvals of a terminated user. It does NOT resolve A6: the manager's 8/28/2025 revoke decision was executed (removed 9/2/2025) but the same privileged access re-appeared with no request/approval evidence. Re-granting privileged access requires a documented request, manager validation and second-level approval (4.2.3.4); PAM Proc. 4.2 requires rejected-but-retained access to be escalated. Removal not sustained = exception.</t>
-        </is>
-      </c>
       <c r="I7" s="8" t="inlineStr">
         <is>
-          <t>Pass only if a ServiceNow/SanIAM access request with manager + 2nd-level approval dated after 9/2/2025 is produced for the re-grant.</t>
+          <t>Revocation timely but not sustained; re-grant approved without a request. The new ISEAdmin membership and the uncorrelated identity add further gaps.</t>
+        </is>
+      </c>
+      <c r="J7" s="8" t="inlineStr">
+        <is>
+          <t>Re-grant and ISEAdmin add requests with approvals; correlate to SanIAM identity (AD employeeNumber 100546248).</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="8" t="inlineStr">
         <is>
-          <t>MIA25172</t>
+          <t>MIA25175</t>
         </is>
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>Juan Hernandez Ruiz</t>
+          <t>Carlos Hernandez Acevedo</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>SOX Mgr 7/27/2026; CyberArk Mgr 8/17/2026</t>
+          <t>Cisco Network Admins REVOKED; removed 09/08/2025 = 6 bd, within SLA. Back in AD 11/25/2025 -&gt; not sustained (A6).</t>
         </is>
       </c>
       <c r="D8" s="8" t="inlineStr">
         <is>
-          <t>Not in Fieldglass request/response - not needed: the exception is the unapproved re-grant, not engagement status.</t>
+          <t>Cisco Network Admins APPROVED - re-grant without request (A5-E3). Also in ISEAdmin, not a member in 2025 Q3 - no request seen.</t>
         </is>
       </c>
       <c r="E8" s="8" t="inlineStr">
         <is>
-          <t>Approved: SOX Mgr 140-142; CyberArk Mgr 467-468; Alero_Consultant_MIA25172 (12 rows) Approved. AD enabled TRUE. No IAMS termination date; identity NOT correlated (Identity = account ID). Prior cycle: REVOKED 8/28/2025, removed 9/2/2025, RE-GRANTED with no request/approval evidence.</t>
+          <t>Approved (SOX 143-145; CyberArk 469-471). Identity not correlated.</t>
         </is>
       </c>
       <c r="F8" s="8" t="inlineStr">
         <is>
-          <t>SUS.IAMS.4.2.1.1 (HR authoritative; accounts fully synchronized with HR); 4.2.3.4; 4.2.5.6 (App Owner attests uncorrelated accounts); 4.2.5.7; PAM Proc. 4.1.1 C3/C4, 4.2</t>
-        </is>
-      </c>
-      <c r="G8" s="9" t="inlineStr">
+          <t>Not requested / not provided</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>SUS.IAMS.4.2.5.7, 4.2.5.21 (30 bd SLA), 4.2.3.4 (re-grant needs request + manager + 2nd-level approval); PAM Proc. 4.1.1 C3-C4, sec. 4.2, sec. 8 step 10; 4.2.1.1, 4.2.5.6</t>
+        </is>
+      </c>
+      <c r="H8" s="9" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
       </c>
-      <c r="H8" s="8" t="inlineStr">
-        <is>
-          <t>Fieldglass email can substantiate that the person behind MIA25172 is an active contingent worker with a valid work order, which supports the business need for access. However (1) the account is uncorrelated in SanIAM, so it was certified by the manager rather than through Application Owner attestation of uncorrelated accounts (4.2.5.6) and is not synchronized with HR (4.2.1.1); (2) the revoke decision of 8/28/2025 was not sustained - access re-granted without documented approval (4.2.3.4). A6 exception stands.</t>
-        </is>
-      </c>
       <c r="I8" s="8" t="inlineStr">
         <is>
-          <t>Pass only with re-grant approval evidence AND correlation of MIA25172 to the Fieldglass worker record (or App Owner attestation as uncorrelated).</t>
+          <t>Same as MIA25172.</t>
+        </is>
+      </c>
+      <c r="J8" s="8" t="inlineStr">
+        <is>
+          <t>Re-grant and ISEAdmin add requests with approvals; correlate identity (AD employeeNumber 100546251).</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>MIA25175</t>
+          <t>X453396</t>
         </is>
       </c>
       <c r="B9" s="8" t="inlineStr">
         <is>
-          <t>Carlos Hernandez Acevedo</t>
+          <t>Juan Fernando Perez Peralta</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
         <is>
-          <t>SOX Mgr 7/27/2026; CyberArk Mgr 8/17/2026</t>
+          <t>Cisco Network Admins + ISEAdmin REVOKED; removed 09/08/2025 = 6 bd, within SLA. Back in AD 11/25/2025 -&gt; not sustained (A6).</t>
         </is>
       </c>
       <c r="D9" s="8" t="inlineStr">
         <is>
-          <t>Not in Fieldglass request/response - not needed: the exception is the unapproved re-grant, not engagement status.</t>
+          <t>Both groups APPROVED - re-grant without request (A5-E3).</t>
         </is>
       </c>
       <c r="E9" s="8" t="inlineStr">
         <is>
-          <t>Approved: SOX Mgr 143-145; CyberArk Mgr 469-471; Alero_Consultant_MIA25175 (12 rows) Approved. AD enabled TRUE. No IAMS termination date; identity NOT correlated. Prior cycle: REVOKED 8/28/2025, removed 9/8/2025, RE-GRANTED with no request/approval evidence.</t>
+          <t>Approved (SOX 110-112; CyberArk 443-445).</t>
         </is>
       </c>
       <c r="F9" s="8" t="inlineStr">
         <is>
-          <t>SUS.IAMS.4.2.1.1; 4.2.3.4; 4.2.5.6; 4.2.5.7; PAM Proc. 4.1.1 C3/C4, 4.2</t>
-        </is>
-      </c>
-      <c r="G9" s="9" t="inlineStr">
+          <t>Not requested / not provided</t>
+        </is>
+      </c>
+      <c r="G9" s="8" t="inlineStr">
+        <is>
+          <t>SUS.IAMS.4.2.5.7, 4.2.5.21 (30 bd SLA), 4.2.3.4 (re-grant needs request + manager + 2nd-level approval); PAM Proc. 4.1.1 C3-C4, sec. 4.2, sec. 8 step 10</t>
+        </is>
+      </c>
+      <c r="H9" s="9" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
       </c>
-      <c r="H9" s="8" t="inlineStr">
-        <is>
-          <t>Same as MIA25172. Fieldglass supports active engagement / business need, but the account is uncorrelated to HR (4.2.1.1, 4.2.5.6) and the 8/28/2025 revocation was not sustained (removed 9/8/2025, then re-granted with no request/approval - 4.2.3.4). A6 exception stands.</t>
-        </is>
-      </c>
       <c r="I9" s="8" t="inlineStr">
         <is>
-          <t>Pass only with re-grant approval evidence AND correlation to the Fieldglass worker record.</t>
+          <t>Revocation timely but not sustained; re-grant approved without a request. Identity correlated, no termination date - engagement status is not the issue.</t>
+        </is>
+      </c>
+      <c r="J9" s="8" t="inlineStr">
+        <is>
+          <t>Netwrix 'member added' event + approved ServiceNow request for the re-grant.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="8" t="inlineStr">
         <is>
-          <t>X453396</t>
+          <t>MIA25103</t>
         </is>
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>Juan Fernando Perez Peralta</t>
+          <t>Ivan Ramirez Gonzalez</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>SOX Mgr 7/27/2026; CyberArk Mgr 8/17/2026</t>
+          <t>Both groups APPROVED while AD account DISABLED; last logon 10/15/2023 (A5-E1). IAMS term 12/31/2024 (E2).</t>
         </is>
       </c>
       <c r="D10" s="8" t="inlineStr">
         <is>
-          <t>Not in Fieldglass request/response - not needed: the exception is the unapproved re-grant, not engagement status.</t>
+          <t>Both groups APPROVED while AD DISABLED (last change 04/02/2026) (A5-E1).</t>
         </is>
       </c>
       <c r="E10" s="8" t="inlineStr">
         <is>
-          <t>Approved: SOX Mgr 110-112; CyberArk Mgr 443-445; Alero_Protect-x453396 (12 rows) Approved. AD enabled TRUE. No IAMS termination date; correlated. Prior cycle: REVOKED 8/28/2025, removed 9/8/2025, RE-GRANTED with no request/approval evidence.</t>
+          <t>Approved again (SOX 86-88; CyberArk 419-421); AD still disabled 10/10/2026.</t>
         </is>
       </c>
       <c r="F10" s="8" t="inlineStr">
         <is>
-          <t>SUS.IAMS.4.2.3.4; 4.2.5.7; 4.2.5.21; PAM Proc. 4.1.1 C3/C4, 4.2</t>
-        </is>
-      </c>
-      <c r="G10" s="9" t="inlineStr">
+          <t>Worker SANWK00016501 OPEN 2024-01-01 - 2027-02-28 (WO SANWO00017798)</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>SUS.IAMS.4.2.5.1 (access must remain valid / least privilege), 4.2.5.7, 4.2.3.1 (inactive accounts disabled or removed); PAM Proc. sec. 8 step 9</t>
+        </is>
+      </c>
+      <c r="H10" s="9" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
       </c>
-      <c r="H10" s="8" t="inlineStr">
-        <is>
-          <t>Identity is correlated and no termination date exists, so Fieldglass adds little to the A5 question - the user is active and the 2026 approvals are appropriate on their face. The exception is A6: the 8/28/2025 revoke was executed (9/8/2025) but access was later re-granted without a documented request and approvals (4.2.3.4). Removal not sustained.</t>
-        </is>
-      </c>
       <c r="I10" s="8" t="inlineStr">
         <is>
-          <t>Pass only with ServiceNow/SanIAM re-grant request + approvals dated after 9/8/2025.</t>
+          <t>Fieldglass clears E2 - he is an active contractor, not a leaver. It does not clear E1: privileged Cisco/ISE admin access on an account disabled and unused since 10/15/2023 was approved in both in-period reviews (and again in 2026 Q2). Access unused for ~2 years is not 'valid and needed' under 4.2.5.1; the reviewer should have revoked it.</t>
+        </is>
+      </c>
+      <c r="J10" s="8" t="inlineStr">
+        <is>
+          <t>Documented business reason accepted by the control owner for retaining privileged access on a disabled, unused account - unlikely; recommend revocation.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>MIA25103</t>
+          <t>MIA25104</t>
         </is>
       </c>
       <c r="B11" s="8" t="inlineStr">
         <is>
-          <t>Ivan Ramirez Gonzalez</t>
+          <t>Jefferson Paez Venegas</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
         <is>
-          <t>SOX Mgr 7/27/2026; CyberArk Mgr 8/17/2026</t>
+          <t>Both groups APPROVED; AD enabled, last logon 11/20/2025. Only issue: IAMS term 12/31/2024 (E2).</t>
         </is>
       </c>
       <c r="D11" s="8" t="inlineStr">
         <is>
-          <t>email from BSI Procurement 10/29/2026. Worker SANWK00016501 OPEN 2024-01-01 - 2027-02-28; current WO SANWO00017798 (Rev.18) Confirmed 2026-09-29 - 2027-02-28; buyer ref 100531048; prior record: SANWK00014976 / WO SANWO00016242 Closed 2023-10-08 - 2023-12-31.</t>
+          <t>Both groups APPROVED; AD enabled (exp. 06/01/2026). Only issue: E2.</t>
         </is>
       </c>
       <c r="E11" s="8" t="inlineStr">
         <is>
-          <t>Approved: SOX Mgr 86-88; CyberArk Mgr 419-421; Alero_Consultant_MIA25103 (12 rows) Approved. AD enabled FALSE (disabled at approval and still disabled 10/10/2026). IAMS term date 12/31/2024, correlated. Never revoked (A6 N/A).</t>
+          <t>Approved (SOX 89-91; CyberArk 422-424); AD enabled 10/10/2026.</t>
         </is>
       </c>
       <c r="F11" s="8" t="inlineStr">
         <is>
-          <t>SUS.IAMS.4.2.1.1; 4.2.3.1 (inactive AD accounts disabled); 4.2.4.2 / 4.2.4.3 + App. G (terminated users: AD 1 business day, privileged 30 business days); 4.2.5.7</t>
-        </is>
-      </c>
-      <c r="G11" s="10" t="inlineStr">
-        <is>
-          <t>PASS (with observation)</t>
-        </is>
-      </c>
-      <c r="H11" s="8" t="inlineStr">
-        <is>
-          <t>Fieldglass (email from BSI Procurement 10/29/2026) shows Worker SANWK00016501 Status OPEN, period 2024-01-01 - 2027-02-28, SGTO_CYBER BAU_PROTECT_2023, Dept GREXT_000079 Cyber Security, supplier Grupo Santander (SGT). The open period covers every relevant date (8/28/2025, 4/30/2026, 7/27/2026 SOX cert, 8/17/2026 CyberArk cert) and no closed worker record or break in 2025-2026 is shown. The SanIAM IAMS Termination Date of 12/31/2024 does not match any Fieldglass engagement end (the only closed record ended 12/31/2023) - it is stale data, not a separation. Under SUS.IAMS.4.2.1.1 HR (Fieldglass for contingent workers) is the authoritative source, so the user was an ACTIVE workforce member when approved; the termination SLAs in 4.2.4.2 / 4.2.4.3 (App. G) were not triggered, and manager approval in both quarterly certifications satisfies SUS.IAMS.4.2.5.6 and PAM Procedure Section 2 / 4.1.1 C2. AD was disabled at approval and remains disabled at 10/10/2026. Because Fieldglass confirms active engagement, the disablement is an inactivity/restrictive state (SUS.IAMS.4.2.3.1), not a missed termination; a disabled AD identity cannot use the CyberArk/Alero access. Observation: account unused/disabled for an extended period - manager should confirm continued need or revoke at next cycle (least privilege, 4.2.5.1). Evidence limitation (does not change the conclusion): screenshots are search-result views without the report run date/parameters, extension history or approvers requested in the 10/14/2026 email; the current work order revision (Rev.18) shows period 2026-09-29 - 2027-02-28 and a Job Seeker submission on 2026-09-29, so the continuity conclusion rests on the OPEN worker record period.</t>
+          <t>Worker SANWK00016508 OPEN 2024-01-01 - 2027-02-28 (WO SANWO00017799)</t>
+        </is>
+      </c>
+      <c r="G11" s="8" t="inlineStr">
+        <is>
+          <t>SUS.IAMS.4.2.1.1 (HR/Fieldglass authoritative), 4.2.5.6, 4.2.5.7; 4.2.4.2/4.2.4.3 not triggered</t>
+        </is>
+      </c>
+      <c r="H11" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="I11" s="8" t="inlineStr">
         <is>
-          <t>Would change to FAIL only if the Fieldglass detail/history shows the engagement ended or lapsed before 8/17/2026 (e.g., if the 2026-09-29 work order was a re-hire after a gap).</t>
+          <t>Fieldglass shows an open engagement covering 8/28/2025 and 4/30/2026, so the 12/31/2024 IAMS date is stale data, not a termination. Active, enabled, recently used account approved by the line manager in both samples. E2 cleared; no exception.</t>
+        </is>
+      </c>
+      <c r="J11" s="8" t="inlineStr">
+        <is>
+          <t>FAIL only if Fieldglass detail shows a lapse in engagement on 8/28/2025 or 4/30/2026.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="8" t="inlineStr">
         <is>
-          <t>MIA25104</t>
+          <t>MIA25105</t>
         </is>
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>Jefferson Paez Venegas</t>
+          <t>David Serrano Aguirre</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>SOX Mgr 7/27/2026; CyberArk Mgr 8/17/2026</t>
+          <t>Both groups APPROVED; AD enabled, last logon 11/18/2025. Only issue: E2.</t>
         </is>
       </c>
       <c r="D12" s="8" t="inlineStr">
         <is>
-          <t>email from BSI Procurement 10/29/2026. Worker SANWK00016508 OPEN 2024-01-01 - 2027-02-28; current WO SANWO00017799 (Rev.18) Confirmed 2026-09-29 - 2027-02-28; buyer ref 100531049; prior record: SANWK00014980 / WO SANWO00016246 Closed 2023-10-08 - 2023-12-31.</t>
+          <t>Both groups APPROVED; AD enabled. Only issue: E2.</t>
         </is>
       </c>
       <c r="E12" s="8" t="inlineStr">
         <is>
-          <t>Approved: SOX Mgr 89-91; CyberArk Mgr 422-424; Alero_Consultant_MIA25104 (12 rows) Approved. AD enabled TRUE. IAMS term date 12/31/2024, correlated. Never revoked (A6 N/A). Prior status: E2 pending Fieldglass.</t>
+          <t>Approved (SOX 92-94; CyberArk 425-427); AD enabled 10/10/2026.</t>
         </is>
       </c>
       <c r="F12" s="8" t="inlineStr">
         <is>
-          <t>SUS.IAMS.4.2.1.1; 4.2.4.1; 4.2.4.3 + App. G; 4.2.5.6; PAM Proc. 2 / 4.1.1 C2</t>
-        </is>
-      </c>
-      <c r="G12" s="10" t="inlineStr">
+          <t>Worker SANWK00016502 OPEN 2024-01-01 - 2027-02-28 (WO SANWO00017797)</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>SUS.IAMS.4.2.1.1, 4.2.5.6, 4.2.5.7</t>
+        </is>
+      </c>
+      <c r="H12" s="10" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="H12" s="8" t="inlineStr">
-        <is>
-          <t>Fieldglass (email from BSI Procurement 10/29/2026) shows Worker SANWK00016508 Status OPEN, period 2024-01-01 - 2027-02-28, SGTO_CYBER BAU_PROTECT_2023, Dept GREXT_000079 Cyber Security, supplier Grupo Santander (SGT). The open period covers every relevant date (8/28/2025, 4/30/2026, 7/27/2026 SOX cert, 8/17/2026 CyberArk cert) and no closed worker record or break in 2025-2026 is shown. The SanIAM IAMS Termination Date of 12/31/2024 does not match any Fieldglass engagement end (the only closed record ended 12/31/2023) - it is stale data, not a separation. Under SUS.IAMS.4.2.1.1 HR (Fieldglass for contingent workers) is the authoritative source, so the user was an ACTIVE workforce member when approved; the termination SLAs in 4.2.4.2 / 4.2.4.3 (App. G) were not triggered, and manager approval in both quarterly certifications satisfies SUS.IAMS.4.2.5.6 and PAM Procedure Section 2 / 4.1.1 C2. The E2 item pending Fieldglass is closed. No exception. Evidence limitation (does not change the conclusion): screenshots are search-result views without the report run date/parameters, extension history or approvers requested in the 10/14/2026 email; the current work order revision (Rev.18) shows period 2026-09-29 - 2027-02-28 and a Job Seeker submission on 2026-09-29, so the continuity conclusion rests on the OPEN worker record period.</t>
-        </is>
-      </c>
       <c r="I12" s="8" t="inlineStr">
         <is>
-          <t>Would change to FAIL only if the Fieldglass detail/history shows the engagement ended or lapsed before 8/17/2026 (e.g., if the 2026-09-29 work order was a re-hire after a gap).</t>
+          <t>Same as MIA25104 - E2 cleared by Fieldglass; no exception in either sample.</t>
+        </is>
+      </c>
+      <c r="J12" s="8" t="inlineStr">
+        <is>
+          <t>FAIL only if Fieldglass detail shows a lapse on a decision date.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t>MIA25105</t>
+          <t>MIA25106</t>
         </is>
       </c>
       <c r="B13" s="8" t="inlineStr">
         <is>
-          <t>David Serrano Aguirre</t>
+          <t>Maiko Vazquez Arias</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
         <is>
-          <t>SOX Mgr 7/27/2026; CyberArk Mgr 8/17/2026</t>
+          <t>Both groups APPROVED; AD enabled, last logon 11/18/2025. Only issue: E2.</t>
         </is>
       </c>
       <c r="D13" s="8" t="inlineStr">
         <is>
-          <t>email from BSI Procurement 10/29/2026. Worker SANWK00016502 OPEN 2024-01-01 - 2027-02-28; current WO SANWO00017797 (Rev.18) Confirmed 2026-09-29 - 2027-02-28; buyer ref 100531050; prior record: SANWK00014979 / WO SANWO00016245 Closed 2023-10-08 - 2023-12-31.</t>
+          <t>Both groups APPROVED; AD enabled. Only issue: E2.</t>
         </is>
       </c>
       <c r="E13" s="8" t="inlineStr">
         <is>
-          <t>Approved: SOX Mgr 92-94; CyberArk Mgr 425-427; Alero_Consultant_MIA25105 (12 rows) Approved. AD enabled TRUE. IAMS term date 12/31/2024, correlated. Never revoked. Prior status: E2 pending Fieldglass.</t>
+          <t>Approved (SOX 95-97; CyberArk 428-430); AD enabled 10/10/2026.</t>
         </is>
       </c>
       <c r="F13" s="8" t="inlineStr">
         <is>
-          <t>SUS.IAMS.4.2.1.1; 4.2.4.1; 4.2.4.3 + App. G; 4.2.5.6; PAM Proc. 2 / 4.1.1 C2</t>
-        </is>
-      </c>
-      <c r="G13" s="10" t="inlineStr">
+          <t>Worker SANWK00016503 OPEN 2024-01-01 - 2027-02-28 (WO SANWO00017800)</t>
+        </is>
+      </c>
+      <c r="G13" s="8" t="inlineStr">
+        <is>
+          <t>SUS.IAMS.4.2.1.1, 4.2.5.6, 4.2.5.7</t>
+        </is>
+      </c>
+      <c r="H13" s="10" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="H13" s="8" t="inlineStr">
-        <is>
-          <t>Fieldglass (email from BSI Procurement 10/29/2026) shows Worker SANWK00016502 Status OPEN, period 2024-01-01 - 2027-02-28, SGTO_CYBER BAU_PROTECT_2023, Dept GREXT_000079 Cyber Security, supplier Grupo Santander (SGT). The open period covers every relevant date (8/28/2025, 4/30/2026, 7/27/2026 SOX cert, 8/17/2026 CyberArk cert) and no closed worker record or break in 2025-2026 is shown. The SanIAM IAMS Termination Date of 12/31/2024 does not match any Fieldglass engagement end (the only closed record ended 12/31/2023) - it is stale data, not a separation. Under SUS.IAMS.4.2.1.1 HR (Fieldglass for contingent workers) is the authoritative source, so the user was an ACTIVE workforce member when approved; the termination SLAs in 4.2.4.2 / 4.2.4.3 (App. G) were not triggered, and manager approval in both quarterly certifications satisfies SUS.IAMS.4.2.5.6 and PAM Procedure Section 2 / 4.1.1 C2. The E2 item pending Fieldglass is closed. No exception. Evidence limitation (does not change the conclusion): screenshots are search-result views without the report run date/parameters, extension history or approvers requested in the 10/14/2026 email; the current work order revision (Rev.18) shows period 2026-09-29 - 2027-02-28 and a Job Seeker submission on 2026-09-29, so the continuity conclusion rests on the OPEN worker record period.</t>
-        </is>
-      </c>
       <c r="I13" s="8" t="inlineStr">
         <is>
-          <t>Would change to FAIL only if the Fieldglass detail/history shows the engagement ended or lapsed before 8/17/2026 (e.g., if the 2026-09-29 work order was a re-hire after a gap).</t>
+          <t>Same as MIA25104 - E2 cleared by Fieldglass; no exception in either sample.</t>
+        </is>
+      </c>
+      <c r="J13" s="8" t="inlineStr">
+        <is>
+          <t>FAIL only if Fieldglass detail shows a lapse on a decision date.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="8" t="inlineStr">
         <is>
-          <t>MIA25106</t>
+          <t>MIA25249</t>
         </is>
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>Maiko Vazquez Arias</t>
+          <t>Richard Harris</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>SOX Mgr 7/27/2026; CyberArk Mgr 8/17/2026</t>
+          <t>Both groups APPROVED; AD enabled, last logon 11/17/2025. Only issue: E2 -&gt; cleared by Fieldglass (PASS for this sample).</t>
         </is>
       </c>
       <c r="D14" s="8" t="inlineStr">
         <is>
-          <t>email from BSI Procurement 10/29/2026. Worker SANWK00016503 OPEN 2024-01-01 - 2027-02-28; current WO SANWO00017800 (Rev.18) Confirmed 2026-09-29 - 2027-02-28; buyer ref 100531051; prior record: SANWK00014977 / WO SANWO00016243 Closed 2023-10-08 - 2023-12-31.</t>
+          <t>Both groups APPROVED on 4/30/2026 while AD DISABLED since 04/02/2026 (A5-E1).</t>
         </is>
       </c>
       <c r="E14" s="8" t="inlineStr">
         <is>
-          <t>Approved: SOX Mgr 95-97; CyberArk Mgr 428-430; Alero_Consultant_MIA25106 (12 rows) Approved. AD enabled TRUE. IAMS term date 12/31/2024, correlated. Never revoked. Prior status: E2 pending Fieldglass.</t>
+          <t>Approved (SOX 104-106; CyberArk 437-439); AD re-ENABLED by 10/10/2026 - no request evidenced.</t>
         </is>
       </c>
       <c r="F14" s="8" t="inlineStr">
         <is>
-          <t>SUS.IAMS.4.2.1.1; 4.2.4.1; 4.2.4.3 + App. G; 4.2.5.6; PAM Proc. 2 / 4.1.1 C2</t>
-        </is>
-      </c>
-      <c r="G14" s="10" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="H14" s="8" t="inlineStr">
-        <is>
-          <t>Fieldglass (email from BSI Procurement 10/29/2026) shows Worker SANWK00016503 Status OPEN, period 2024-01-01 - 2027-02-28, SGTO_CYBER BAU_PROTECT_2023, Dept GREXT_000079 Cyber Security, supplier Grupo Santander (SGT). The open period covers every relevant date (8/28/2025, 4/30/2026, 7/27/2026 SOX cert, 8/17/2026 CyberArk cert) and no closed worker record or break in 2025-2026 is shown. The SanIAM IAMS Termination Date of 12/31/2024 does not match any Fieldglass engagement end (the only closed record ended 12/31/2023) - it is stale data, not a separation. Under SUS.IAMS.4.2.1.1 HR (Fieldglass for contingent workers) is the authoritative source, so the user was an ACTIVE workforce member when approved; the termination SLAs in 4.2.4.2 / 4.2.4.3 (App. G) were not triggered, and manager approval in both quarterly certifications satisfies SUS.IAMS.4.2.5.6 and PAM Procedure Section 2 / 4.1.1 C2. The E2 item pending Fieldglass is closed. No exception. Evidence limitation (does not change the conclusion): screenshots are search-result views without the report run date/parameters, extension history or approvers requested in the 10/14/2026 email; the current work order revision (Rev.18) shows period 2026-09-29 - 2027-02-28 and a Job Seeker submission on 2026-09-29, so the continuity conclusion rests on the OPEN worker record period.</t>
+          <t>Worker SANWK00016311 OPEN 2023-12-28 - 2027-02-28 (WO SANWO00017821)</t>
+        </is>
+      </c>
+      <c r="G14" s="8" t="inlineStr">
+        <is>
+          <t>SUS.IAMS.4.2.5.1, 4.2.5.7, 4.2.3.1; 4.2.3.4 (re-enable of privileged account)</t>
+        </is>
+      </c>
+      <c r="H14" s="9" t="inlineStr">
+        <is>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="I14" s="8" t="inlineStr">
         <is>
-          <t>Would change to FAIL only if the Fieldglass detail/history shows the engagement ended or lapsed before 8/17/2026 (e.g., if the 2026-09-29 work order was a re-hire after a gap).</t>
+          <t>2025 Q3 passes once Fieldglass clears E2. 2026 Q1 fails: the account was disabled 04/02/2026 and its privileged access was approved 4/30/2026 without the reviewer addressing the disabled status. Fieldglass shows the engagement record open, so this was not a termination, but it does not explain the disablement (one of 9 contractor accounts disabled 4/2-4/3/2026), and the later re-enable is unevidenced.</t>
+        </is>
+      </c>
+      <c r="J14" s="8" t="inlineStr">
+        <is>
+          <t>Evidence of why the 9 accounts were disabled on 4/2-4/3/2026 (e.g., expiry/batch action) plus an approved re-enable request could reduce E1 to an observation.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="8" t="inlineStr">
         <is>
-          <t>MIA25249</t>
+          <t>MIA25250</t>
         </is>
       </c>
       <c r="B15" s="8" t="inlineStr">
         <is>
-          <t>Richard Harris</t>
+          <t>Kevin Ackley</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
         <is>
-          <t>SOX Mgr 7/27/2026; CyberArk Mgr 8/17/2026</t>
+          <t>Both groups APPROVED; AD enabled, last logon 11/07/2025. Only issue: E2 -&gt; cleared by Fieldglass (PASS for this sample).</t>
         </is>
       </c>
       <c r="D15" s="8" t="inlineStr">
         <is>
-          <t>email from BSI Procurement 10/29/2026. Worker SANWK00016311 OPEN 2023-12-28 - 2027-02-28; current WO SANWO00017821 (Rev.18) Confirmed 2026-09-29 - 2027-02-28; buyer ref 100592069; prior record: None shown.</t>
+          <t>Both groups APPROVED on 4/30/2026 while AD DISABLED since 04/03/2026 (A5-E1).</t>
         </is>
       </c>
       <c r="E15" s="8" t="inlineStr">
         <is>
-          <t>Approved: SOX Mgr 104-106; CyberArk Mgr 437-439; Alero_Consultant_MIA25249 (12 rows) Approved. AD FALSE on 05/15/2026, TRUE on 10/10/2026 (re-enabled). IAMS term date 12/31/2024, correlated. Never revoked.</t>
+          <t>Approved (SOX 101-103; CyberArk 434-436); AD re-ENABLED by 10/10/2026 - no request evidenced; AD employeeNumber blank.</t>
         </is>
       </c>
       <c r="F15" s="8" t="inlineStr">
         <is>
-          <t>SUS.IAMS.4.2.1.1; 4.2.3.1; 4.2.4.2 / 4.2.4.3 + App. G; 4.2.5.6</t>
-        </is>
-      </c>
-      <c r="G15" s="10" t="inlineStr">
-        <is>
-          <t>PASS (with observation)</t>
-        </is>
-      </c>
-      <c r="H15" s="8" t="inlineStr">
-        <is>
-          <t>Fieldglass (email from BSI Procurement 10/29/2026) shows Worker SANWK00016311 Status OPEN, period 2023-12-28 - 2027-02-28, SGTO_CYBER BAU_PROTECT_2023, Dept GREXT_000079 Cyber Security, supplier Grupo Santander (SGT). The open period covers every relevant date (8/28/2025, 4/30/2026, 7/27/2026 SOX cert, 8/17/2026 CyberArk cert) and no closed worker record or break in 2025-2026 is shown. The SanIAM IAMS Termination Date of 12/31/2024 does not match any Fieldglass engagement end (the only closed record ended 12/31/2023) - it is stale data, not a separation. Under SUS.IAMS.4.2.1.1 HR (Fieldglass for contingent workers) is the authoritative source, so the user was an ACTIVE workforce member when approved; the termination SLAs in 4.2.4.2 / 4.2.4.3 (App. G) were not triggered, and manager approval in both quarterly certifications satisfies SUS.IAMS.4.2.5.6 and PAM Procedure Section 2 / 4.1.1 C2. AD FALSE on 05/15/2026 and TRUE on 10/10/2026: Fieldglass shows no engagement end or gap in April-May 2026, so the disablement was not a termination (4.2.3.1 inactivity) and approval of an active contractor's access was appropriate. Observation: obtain the AD re-enable ticket to evidence the re-activation was authorized. Note: Fieldglass also lists an Active Santander US employee 'Harris, Richard (n222712)', Hiring Manager, Cyber Security Engineering - confirm identity link (not needed for the conclusion). Evidence limitation (does not change the conclusion): screenshots are search-result views without the report run date/parameters, extension history or approvers requested in the 10/14/2026 email; the current work order revision (Rev.18) shows period 2026-09-29 - 2027-02-28 and a Job Seeker submission on 2026-09-29, so the continuity conclusion rests on the OPEN worker record period.</t>
+          <t>Worker SANWK00016313 OPEN 2023-12-28 - 2027-02-28 (WO SANWO00017820)</t>
+        </is>
+      </c>
+      <c r="G15" s="8" t="inlineStr">
+        <is>
+          <t>SUS.IAMS.4.2.5.1, 4.2.5.7, 4.2.3.1, 4.2.3.4, 4.2.1.1 (sync with HR)</t>
+        </is>
+      </c>
+      <c r="H15" s="9" t="inlineStr">
+        <is>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="I15" s="8" t="inlineStr">
         <is>
-          <t>Would change to FAIL only if the Fieldglass detail/history shows the engagement ended or lapsed before 8/17/2026 (e.g., if the 2026-09-29 work order was a re-hire after a gap).</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="8" t="inlineStr">
-        <is>
-          <t>MIA25250</t>
-        </is>
-      </c>
-      <c r="B16" s="8" t="inlineStr">
-        <is>
-          <t>Kevin Ackley</t>
-        </is>
-      </c>
-      <c r="C16" s="8" t="inlineStr">
-        <is>
-          <t>SOX Mgr 7/27/2026; CyberArk Mgr 8/17/2026</t>
-        </is>
-      </c>
-      <c r="D16" s="8" t="inlineStr">
-        <is>
-          <t>email from BSI Procurement 10/29/2026. Worker SANWK00016313 OPEN 2023-12-28 - 2027-02-28; current WO SANWO00017820 (Rev.18) Confirmed 2026-09-29 - 2027-02-28; buyer ref 100592068; prior record: None shown.</t>
-        </is>
-      </c>
-      <c r="E16" s="8" t="inlineStr">
-        <is>
-          <t>Approved: SOX Mgr 101-103; CyberArk Mgr 434-436; Alero_Protect-MIA25250 (12 rows) Approved. AD FALSE on 05/15/2026, TRUE on 10/10/2026. IAMS term date 12/31/2024, correlated in cert; AD employeeNumber BLANK. Never revoked.</t>
-        </is>
-      </c>
-      <c r="F16" s="8" t="inlineStr">
-        <is>
-          <t>SUS.IAMS.4.2.1.1 (accounts fully synchronized with HR); 4.2.3.1; 4.2.4.2 / 4.2.4.3 + App. G; 4.2.5.6</t>
-        </is>
-      </c>
-      <c r="G16" s="10" t="inlineStr">
-        <is>
-          <t>PASS (with observation)</t>
-        </is>
-      </c>
-      <c r="H16" s="8" t="inlineStr">
-        <is>
-          <t>Fieldglass (email from BSI Procurement 10/29/2026) shows Worker SANWK00016313 Status OPEN, period 2023-12-28 - 2027-02-28, SGTO_CYBER BAU_PROTECT_2023, Dept GREXT_000079 Cyber Security, supplier Grupo Santander (SGT). The open period covers every relevant date (8/28/2025, 4/30/2026, 7/27/2026 SOX cert, 8/17/2026 CyberArk cert) and no closed worker record or break in 2025-2026 is shown. The SanIAM IAMS Termination Date of 12/31/2024 does not match any Fieldglass engagement end (the only closed record ended 12/31/2023) - it is stale data, not a separation. Under SUS.IAMS.4.2.1.1 HR (Fieldglass for contingent workers) is the authoritative source, so the user was an ACTIVE workforce member when approved; the termination SLAs in 4.2.4.2 / 4.2.4.3 (App. G) were not triggered, and manager approval in both quarterly certifications satisfies SUS.IAMS.4.2.5.6 and PAM Procedure Section 2 / 4.1.1 C2. AD FALSE on 05/15/2026 and TRUE on 10/10/2026: no engagement end or gap shown, so not a termination. Observations: (1) AD employeeNumber is blank - populate the Fieldglass worker ID so AD is synchronized with HR (4.2.1.1); (2) obtain the AD re-enable ticket. Fieldglass also lists Workforce ID SGTOWF00003892 and an Active employee 'Ackley, Kevin (n67450)', Cyber Security Engineering - confirm identity link. Evidence limitation (does not change the conclusion): screenshots are search-result views without the report run date/parameters, extension history or approvers requested in the 10/14/2026 email; the current work order revision (Rev.18) shows period 2026-09-29 - 2027-02-28 and a Job Seeker submission on 2026-09-29, so the continuity conclusion rests on the OPEN worker record period.</t>
-        </is>
-      </c>
-      <c r="I16" s="8" t="inlineStr">
-        <is>
-          <t>Would change to FAIL only if the Fieldglass detail/history shows the engagement ended or lapsed before 8/17/2026 (e.g., if the 2026-09-29 work order was a re-hire after a gap).</t>
-        </is>
-      </c>
-    </row>
-    <row r="17"/>
+          <t>Same as MIA25249: 2025 Q3 passes with Fieldglass; 2026 Q1 fails on approval of a disabled account, with an unevidenced re-enable. Blank AD employeeNumber is an additional data-sync observation.</t>
+        </is>
+      </c>
+      <c r="J15" s="8" t="inlineStr">
+        <is>
+          <t>Same as MIA25249; also populate employeeNumber.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Summary: 3 PASS (MIA25104, MIA25105, MIA25106); 7 FAIL - A6 not sustained + A5-E3 re-grant (MIA25142, MIA25172, MIA25175, X453396); A5-E1 disabled accounts approved (MIA25103 both samples; MIA25249, MIA25250 in 2026 Q1).</t>
+        </is>
+      </c>
+    </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Summary: 6 PASS based on Fieldglass (MIA25104, MIA25105, MIA25106 clean; MIA25103, MIA25249, MIA25250 with observations); 4 FAIL - A6 removal not sustained (MIA25142, MIA25172, MIA25175, X453396). Fieldglass also covered MIA25251 Ashish Rimal (not in this sample).</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Overall observation: SanIAM IAMS termination date 12/31/2024 matches no Fieldglass engagement end (open records run to 2027-02-28; prior closed records ended 12/31/2023) - SanIAM is not synchronized with Fieldglass (SUS.IAMS.4.2.1.1). Recommend a Fieldglass-to-SanIAM end-date reconciliation.</t>
+          <t>Correction vs. earlier version: MIA25103, MIA25249 and MIA25250 changed from PASS to FAIL after testing against the in-period 2025 Q3 and 2026 Q1 certifications. Fieldglass clears E2 (IAMS termination date) for the six contractors but does not clear E1 (approval of AD-disabled accounts).</t>
         </is>
       </c>
     </row>
